--- a/Figure S3/Figure S3-B.xlsx
+++ b/Figure S3/Figure S3-B.xlsx
@@ -1,96 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\附图3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure S2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB439F7-AD58-4A8C-8764-FB8559C03FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A03932F-A220-4777-997F-273274E13DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15290" yWindow="1090" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>CON 1</t>
-  </si>
-  <si>
-    <t>CON 2</t>
-  </si>
-  <si>
-    <t>CON 3</t>
-  </si>
-  <si>
-    <t>CON 4</t>
-  </si>
-  <si>
-    <t>CON 5</t>
-  </si>
-  <si>
-    <t>ETEC 1</t>
-  </si>
-  <si>
-    <t>ETEC 2</t>
-  </si>
-  <si>
-    <t>ETEC 3</t>
-  </si>
-  <si>
-    <t>ETEC 4</t>
-  </si>
-  <si>
-    <t>EWK 1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>pValue</t>
+  </si>
+  <si>
+    <t>VIPscore</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>ETEC</t>
+  </si>
+  <si>
+    <t>ETEC_WB800</t>
+  </si>
+  <si>
+    <t>ETEC_WB800_KR32</t>
+  </si>
+  <si>
+    <t>Cadralazine</t>
+  </si>
+  <si>
+    <t>(2R)-2-{[(4R)-4-{[(2S)-2-{[(2R)-2-{[(2R,3R,4R,5S,6R)-3-Acetamido-2,5-dihydroxy-6-(hydroxymethyl)tetrahydro-2H-pyran-4-yl]oxy}propanoyl]amino}propanoyl]amino}-5-amino-5-oxopentanoyl]amino}-6-(stearoyla
+mino)hexanoic acid</t>
+  </si>
+  <si>
+    <t>O-[{(2R)-2-[(13Z,16Z)-13,16-Docosadienoyloxy]-3-[(9Z)-9-octadecenoyloxy]propoxy}(hydroxy)phosphoryl]-L-serine</t>
+  </si>
+  <si>
+    <t>6-hydroxy-1H-indole-3-acetamide</t>
+  </si>
+  <si>
+    <t>Margaric acid</t>
+  </si>
+  <si>
+    <t>(2R)-1-(Hexadecyloxy)-3-[(3-O-sulfo-beta-D-galactopyranosyl)oxy]-2-propanyl stearate</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>pentamidine</t>
+  </si>
+  <si>
+    <t>MFCD00037215</t>
+  </si>
+  <si>
+    <t>6-Hydroxycaproic acid</t>
+  </si>
+  <si>
+    <t>azolimine</t>
+  </si>
+  <si>
+    <t>2,3-Dinor-6-keto-PGF1?</t>
+  </si>
+  <si>
+    <t>4-Hydroxy-1H-indole-3-acetonitrile</t>
+  </si>
+  <si>
+    <t>4-Undecylbenzenesulfonic acid</t>
+  </si>
+  <si>
+    <t>Piperonyl sulfoxide</t>
+  </si>
+  <si>
+    <t>[FAoxo_trihydrox]6-oxo-9S_11R_15S-trihydroxy-13E-prostenoicacid</t>
+  </si>
+  <si>
+    <t>Xanthine</t>
+  </si>
+  <si>
+    <t>4-Dodecylbenzenesulfonic acid</t>
+  </si>
+  <si>
+    <t>1_3-Dihydroxy-N-methylacridone</t>
+  </si>
+  <si>
+    <t>Alanine</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EWK 2</t>
-  </si>
-  <si>
-    <t>EWK 3</t>
-  </si>
-  <si>
-    <t>EWK 4</t>
-  </si>
-  <si>
-    <t>EWK 5</t>
-  </si>
-  <si>
-    <t>miR1231-3P</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,11 +160,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -134,7 +192,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -176,12 +234,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -211,12 +269,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -386,134 +444,470 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:21" ht="350" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>0.65</v>
+        <v>7.5348316857142897E-2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.39040843057142899</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.72363309357142902</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1.60513666328571</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.44061319157142798</v>
+      </c>
+      <c r="G2" s="1">
+        <v>13.471276899428601</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.10334628442857099</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.26237905128571398</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.3514910401428599</v>
+      </c>
+      <c r="K2" s="1">
+        <v>8.4180821428571403E-2</v>
+      </c>
+      <c r="L2" s="1">
+        <v>29.1463491585714</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0.26883347200000002</v>
+      </c>
+      <c r="N2" s="1">
+        <v>6.7146945622857102</v>
+      </c>
+      <c r="O2" s="1">
+        <v>2.9515628775714302</v>
+      </c>
+      <c r="P2" s="1">
+        <v>177.96307733714301</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>4.9230921578571403</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0.120754876571429</v>
+      </c>
+      <c r="S2" s="1">
+        <v>19.5849023642857</v>
+      </c>
+      <c r="T2" s="1">
+        <v>74.622147858571395</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.13236336700000001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>7.3875231285714299E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.36314982042857102</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.58181389357142899</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.3901825404285699</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.281844534857143</v>
+      </c>
+      <c r="G3" s="1">
+        <v>11.898094964142899</v>
+      </c>
+      <c r="H3" s="1">
+        <v>9.6876396714285704E-2</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.38650703628571398</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.81016840228571396</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.24262610114285699</v>
+      </c>
+      <c r="L3" s="1">
+        <v>31.060372625714301</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.154485202571429</v>
+      </c>
+      <c r="N3" s="1">
+        <v>2.02654243885714</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2.6225019317142899</v>
+      </c>
+      <c r="P3" s="1">
+        <v>49.713725802857098</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1.1505829999999999</v>
+      </c>
+      <c r="R3" s="1">
+        <v>4.36068978571428E-2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>10.2532773005714</v>
+      </c>
+      <c r="T3" s="1">
+        <v>23.3077577287143</v>
+      </c>
+      <c r="U3" s="1">
+        <v>9.3917271571428596E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.121820828714286</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.43157554757142902</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.72755860714285703</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.8894627487142901</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.440087077142857</v>
+      </c>
+      <c r="G4" s="1">
+        <v>11.257187147428599</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.104459724</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.49988680042857098</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.496278558714286</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.18971202714285701</v>
+      </c>
+      <c r="L4" s="1">
+        <v>30.193150951428599</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.404952848714286</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2.3302613182857099</v>
+      </c>
+      <c r="O4" s="1">
+        <v>5.1516564402857101</v>
+      </c>
+      <c r="P4" s="1">
+        <v>77.240747892857101</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1.76961720228571</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.22253514199999999</v>
+      </c>
+      <c r="S4" s="1">
+        <v>10.4651962487143</v>
+      </c>
+      <c r="T4" s="1">
+        <v>39.492843384428603</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.138029257285714</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.18320029326241699</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10.9985427344635</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.35721222507677</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2.8596103013895</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.71415493054623003</v>
+      </c>
+      <c r="G5" s="1">
+        <v>24.718095660469402</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.23532881928800201</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.49334456301732998</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.30463696271790303</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.318640615257407</v>
+      </c>
+      <c r="L5" s="1">
+        <v>43.7313475704333</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.412611121271869</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1.7243484501580899</v>
+      </c>
+      <c r="O5" s="1">
+        <v>4.95108564485004</v>
+      </c>
+      <c r="P5" s="1">
+        <v>43.451273245178299</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1.04498152714526</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.28423133162241598</v>
+      </c>
+      <c r="S5" s="1">
+        <v>10.928282124603101</v>
+      </c>
+      <c r="T5" s="1">
+        <v>25.108571461634501</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.14671205833498999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.68</v>
+      <c r="B6" s="1">
+        <v>9.5683709933266502E-4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.7278196708363499E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.23746266141781E-2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3.5600495115991802E-2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3.5342233698403502E-3</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3.3573037554148299E-3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2.45008903040136E-2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3.8937722138641301E-2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.3143612743222699E-2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.7311671059257201E-2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>4.20168934659906E-2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>3.0353611749564299E-3</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3.7197134264711898E-2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>4.76238868003548E-2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>4.0142021426405501E-2</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>4.1069022162055498E-2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3.8495262979329897E-2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1.02837898248807E-2</v>
+      </c>
+      <c r="T6" s="1">
+        <v>4.86266630763049E-2</v>
+      </c>
+      <c r="U6" s="1">
+        <v>4.4254106799193199E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
       <c r="B7" s="1">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.32</v>
+        <v>3.9123999999999999</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3.3795000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2.9752999999999998</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.9304999999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.8908</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2.8746</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2.8043999999999998</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2.7856999999999998</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2.7387999999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2.6507000000000001</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2.6431</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2.6301999999999999</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2.5478000000000001</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2.5322</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2.4664000000000001</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2.4537</v>
+      </c>
+      <c r="R7" s="1">
+        <v>2.3151999999999999</v>
+      </c>
+      <c r="S7" s="1">
+        <v>2.2953999999999999</v>
+      </c>
+      <c r="T7" s="1">
+        <v>2.2951999999999999</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2.2599999999999998</v>
       </c>
     </row>
   </sheetData>
